--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N171_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N171_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.04936945613974</v>
+        <v>7.158022536622709</v>
       </c>
       <c r="D2" t="n">
-        <v>43.29191863566196</v>
+        <v>7.034936778295068</v>
       </c>
       <c r="E2" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F2" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.33576731672073</v>
+        <v>5.41706218896712</v>
       </c>
       <c r="D3" t="n">
-        <v>34.18444823595645</v>
+        <v>5.554972838342923</v>
       </c>
       <c r="E3" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F3" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.63398381573067</v>
+        <v>3.353022370056234</v>
       </c>
       <c r="D4" t="n">
-        <v>21.20816466022221</v>
+        <v>3.44632675728611</v>
       </c>
       <c r="E4" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F4" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.59702013297396</v>
+        <v>2.697015771608269</v>
       </c>
       <c r="D5" t="n">
-        <v>16.24218884893128</v>
+        <v>2.639355687951333</v>
       </c>
       <c r="E5" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F5" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.5552283794925</v>
+        <v>5.452724611667531</v>
       </c>
       <c r="D6" t="n">
-        <v>32.73262966023613</v>
+        <v>5.319052319788371</v>
       </c>
       <c r="E6" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F6" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.5415596922323</v>
+        <v>5.77550344998775</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20596431200255</v>
+        <v>5.070969200700414</v>
       </c>
       <c r="E7" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F7" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.20488544843133</v>
+        <v>4.745793885370091</v>
       </c>
       <c r="D8" t="n">
-        <v>34.94187216266964</v>
+        <v>5.678054226433817</v>
       </c>
       <c r="E8" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F8" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.08818033113586</v>
+        <v>3.426829303809577</v>
       </c>
       <c r="D9" t="n">
-        <v>15.82634793276356</v>
+        <v>2.571781539074079</v>
       </c>
       <c r="E9" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F9" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.4522685435753</v>
+        <v>3.648493638330987</v>
       </c>
       <c r="D10" t="n">
-        <v>7.792255321489332</v>
+        <v>1.266241489742016</v>
       </c>
       <c r="E10" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F10" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.34106503838495</v>
+        <v>3.467923068737555</v>
       </c>
       <c r="D11" t="n">
-        <v>17.69956688907572</v>
+        <v>2.876179619474804</v>
       </c>
       <c r="E11" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F11" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.61527114602222</v>
+        <v>5.462481561228611</v>
       </c>
       <c r="D12" t="n">
-        <v>18.15031502409621</v>
+        <v>2.949426191415635</v>
       </c>
       <c r="E12" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F12" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.33764285495105</v>
+        <v>5.579866963929546</v>
       </c>
       <c r="D13" t="n">
-        <v>24.14349420944457</v>
+        <v>3.923317809034743</v>
       </c>
       <c r="E13" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F13" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.3479049425631</v>
+        <v>4.769034553166504</v>
       </c>
       <c r="D14" t="n">
-        <v>33.1618354932663</v>
+        <v>5.388798267655774</v>
       </c>
       <c r="E14" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F14" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.56071119327058</v>
+        <v>3.01611556890647</v>
       </c>
       <c r="D15" t="n">
-        <v>18.92700039036436</v>
+        <v>3.075637563434208</v>
       </c>
       <c r="E15" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F15" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.94341641605066</v>
+        <v>7.303305167608232</v>
       </c>
       <c r="D16" t="n">
-        <v>61.85506343753315</v>
+        <v>10.05144780859914</v>
       </c>
       <c r="E16" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F16" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.06931099959265</v>
+        <v>2.936263037433806</v>
       </c>
       <c r="D17" t="n">
-        <v>18.17249223024055</v>
+        <v>2.95302998741409</v>
       </c>
       <c r="E17" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F17" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.05666999038411</v>
+        <v>6.834208873437418</v>
       </c>
       <c r="D18" t="n">
-        <v>39.06759730250272</v>
+        <v>6.348484561656692</v>
       </c>
       <c r="E18" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F18" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.09188309203678</v>
+        <v>3.102431002455978</v>
       </c>
       <c r="D19" t="n">
-        <v>18.75656097340902</v>
+        <v>3.047941158178965</v>
       </c>
       <c r="E19" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F19" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9.617692030835672</v>
+        <v>1.562874955010797</v>
       </c>
       <c r="D20" t="n">
-        <v>9.541716402562681</v>
+        <v>1.550528915416436</v>
       </c>
       <c r="E20" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F20" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>5.830951894845301</v>
+        <v>0.9475296829123614</v>
       </c>
       <c r="D21" t="n">
-        <v>6.503254522668514</v>
+        <v>1.056778859933634</v>
       </c>
       <c r="E21" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F21" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>39.54320055044822</v>
+        <v>6.425770089447836</v>
       </c>
       <c r="D22" t="n">
-        <v>39.32990726379436</v>
+        <v>6.391109930366584</v>
       </c>
       <c r="E22" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F22" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>3.132507952773453</v>
+        <v>0.5090325423256861</v>
       </c>
       <c r="D23" t="n">
-        <v>3.193475387773125</v>
+        <v>0.5189397505131328</v>
       </c>
       <c r="E23" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F23" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>10.90942070384593</v>
+        <v>1.772780864374964</v>
       </c>
       <c r="D24" t="n">
-        <v>10.73417189074771</v>
+        <v>1.744302932246503</v>
       </c>
       <c r="E24" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F24" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>27.39605951938969</v>
+        <v>4.451859671900825</v>
       </c>
       <c r="D25" t="n">
-        <v>27.27212842351464</v>
+        <v>4.431720868821129</v>
       </c>
       <c r="E25" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F25" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>11.52200451088984</v>
+        <v>1.872325733019599</v>
       </c>
       <c r="D26" t="n">
-        <v>11.60132553313303</v>
+        <v>1.885215399134117</v>
       </c>
       <c r="E26" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F26" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>23.87639477212555</v>
+        <v>3.879914150470401</v>
       </c>
       <c r="D27" t="n">
-        <v>24.08768611483937</v>
+        <v>3.914248993661398</v>
       </c>
       <c r="E27" t="n">
-        <v>11.49174773124807</v>
+        <v>1.867409006327811</v>
       </c>
       <c r="F27" t="n">
-        <v>13.22755269955229</v>
+        <v>2.149477313677247</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
